--- a/Offline_Lasso/result.xlsx
+++ b/Offline_Lasso/result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://keiojp0-my.sharepoint.com/personal/akira_takakura_keio_jp/Documents/Research/Nozaki_Lab/simulations/research_tools/Offline_Lasso/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_AD4D066CA252ABDACC10485C71D1F6DC72EEDF50" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E478C7B4-275F-4BD0-B75A-927831B07C92}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="11_AD4D066CA252ABDACC10485C71D1F6DC72EEDF50" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29C458D3-A092-4396-9308-C456148414D7}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,30 +20,19 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -58,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>x</t>
     <phoneticPr fontId="1"/>
@@ -69,10 +58,6 @@
   </si>
   <si>
     <t>ddx</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>c</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -87,11 +72,23 @@
     <t>dx2</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bias</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="181" formatCode="0.00000000"/>
+    <numFmt numFmtId="184" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -116,7 +113,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -124,12 +121,71 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -145,6 +201,1684 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>x</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$3:$A$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1E-8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9999999999999995E-8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9999999999999995E-7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0000000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$3:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1558.3527200000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1868.72891</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1865.07665</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1827.4968699999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1451.9528</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7D7F-41F2-82D1-1FB1B3E2A4D5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>dx</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$3:$A$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1E-8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9999999999999995E-8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9999999999999995E-7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0000000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$3:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>-0.56640000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2005572099999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4003410000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4874000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.3563700000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.8245439999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7D7F-41F2-82D1-1FB1B3E2A4D5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ddx</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$3:$A$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1E-8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9999999999999995E-8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9999999999999995E-7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0000000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>4.9467306099999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5624499999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4715499999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.0791151299999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-9.1025904899999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.45877328000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.44336362000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.35732999999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7D7F-41F2-82D1-1FB1B3E2A4D5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>x2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$3:$A$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1E-8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9999999999999995E-8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9999999999999995E-7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0000000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$3:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>127144.97199999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7D7F-41F2-82D1-1FB1B3E2A4D5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>xdx</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$3:$A$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1E-8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9999999999999995E-8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9999999999999995E-7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0000000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>871.63761899999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>111.3878</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-7D7F-41F2-82D1-1FB1B3E2A4D5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>dx2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$3:$A$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1E-8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9999999999999995E-8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9999999999999995E-7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0000000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$3:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>-1.54187E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-7.0461227499999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-6.9460646000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-5.5699E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.0907700000000006E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.9631200000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.3361020000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.299486E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-7D7F-41F2-82D1-1FB1B3E2A4D5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$H$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>bias</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$3:$A$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1E-8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9999999999999995E-8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9999999999999995E-7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0000000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$3:$H$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>-7.8563480000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.21468116600000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.2087503</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.14857500000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.45287074500000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.7799629549999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.7877969</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.8361000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.8521299999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-7D7F-41F2-82D1-1FB1B3E2A4D5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2079596015"/>
+        <c:axId val="2079596495"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2079596015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00000000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2079596495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2079596495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2079596015"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>681037</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>452437</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60B8720D-4CF9-F209-2ABD-634A82D3BA68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -410,73 +2144,311 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:H4"/>
+  <dimension ref="A2:H16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="5.75" customWidth="1"/>
+    <col min="1" max="1" width="11.375" customWidth="1"/>
+    <col min="2" max="2" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H2" t="s">
-        <v>6</v>
+      <c r="H2" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" cm="1">
-        <f t="array" ref="A3">10^{-8}</f>
+      <c r="A3" s="5">
+        <f>10^{-8}</f>
         <v>1E-8</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>1558.3527200000001</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>-0.56640000000000001</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>4.9467306099999997E-2</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
+      <c r="E3" s="1">
         <v>127144.97199999999</v>
       </c>
-      <c r="G3">
+      <c r="F3" s="1">
         <v>871.63761899999997</v>
       </c>
-      <c r="H3">
+      <c r="G3" s="1">
         <v>-1.54187E-2</v>
+      </c>
+      <c r="H3" s="1">
+        <v>-7.8563480000000005E-2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" cm="1">
+      <c r="A4" s="5" cm="1">
         <f t="array" ref="A4">10^{-7}</f>
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="E4">
-        <v>0</v>
+      <c r="B4" s="1">
+        <v>1868.72891</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1.2005572099999999</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1.5624499999999999E-2</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>111.3878</v>
+      </c>
+      <c r="G4" s="1">
+        <v>-7.0461227499999998E-3</v>
+      </c>
+      <c r="H4" s="1">
+        <v>-0.21468116600000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="5" cm="1">
+        <f t="array" ref="A5">10^{-6}</f>
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1865.07665</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1.4003410000000001</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.4715499999999999E-2</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>-6.9460646000000003E-3</v>
+      </c>
+      <c r="H5" s="1">
+        <v>-0.2087503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="5" cm="1">
+        <f t="array" ref="A6">10^{-5}</f>
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1827.4968699999999</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.4874000000000001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5.0791151299999998E-3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>-5.5699E-3</v>
+      </c>
+      <c r="H6" s="1">
+        <v>-0.14857500000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="5" cm="1">
+        <f t="array" ref="A7">10^{-4}</f>
+        <v>1E-4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1451.9528</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.3563700000000001</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-9.1025904899999996E-2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>8.0907700000000006E-3</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.45287074500000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3.8245439999999999</v>
+      </c>
+      <c r="D8" s="1">
+        <v>-0.45877328000000001</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>5.9631200000000002E-2</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2.7799629549999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>-0.44336362000000001</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>5.3361020000000002E-2</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2.7877969</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>-0.35732999999999998</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.299486E-2</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2.8361000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="6">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2.8521299999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>5.5385299799999999</v>
+      </c>
+      <c r="D16">
+        <v>-0.46230153000000002</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>6.0815760000000003E-2</v>
+      </c>
+      <c r="H16">
+        <v>2.77834</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>